--- a/Iwaniuk_etal_2001/Iwaniuk_etal_2001.xlsx
+++ b/Iwaniuk_etal_2001/Iwaniuk_etal_2001.xlsx
@@ -20279,8 +20279,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -20542,10 +20542,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2174A131-0224-499D-B6E3-7A87F3253FA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64DF5B83-5B62-4B1C-8A5F-513CCED9A845}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A8EE787-8ABC-415D-9405-8346D3C2BB06}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE95FA9B-6198-4921-9C36-DC28E4D7826D}"/>
 </file>